--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -848,12 +848,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>초안 v0.1</t>
+          <t>초안 v0.2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>01_제안서/</t>
+          <t>01_제안서/ — B2B 디자인 적용 (12슬라이드)</t>
         </is>
       </c>
     </row>

--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -848,12 +848,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>초안 v0.2</t>
+          <t>초안 v0.3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>01_제안서/ — B2B 디자인 적용 (12슬라이드)</t>
+          <t>01_제안서/ — 라이트 컨설팅 스타일 (12슬라이드)</t>
         </is>
       </c>
     </row>

--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1068,32 +1068,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RP-01</t>
+          <t>IN-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>공통 보고</t>
+          <t>내부</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>착수</t>
+          <t>계약 준비</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>착수 보고서</t>
+          <t>계약 가이드라인 (CUPIA 계약관리 시행세칙 적용 기준)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>pptx/docx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>계약 협상 전</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7.3조</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>세칙 제3~12조·제33조</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>초안 v0.1</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>06_보고서/ — 협의사항 합의 내용 반영</t>
+          <t>08_계약관리/ — 세칙 원문은 reference/04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RP-02</t>
+          <t>RP-01</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>착수</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>중간 보고서</t>
+          <t>착수 보고서</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 10.3조(중간 검수)</t>
+          <t>7.3조</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1165,14 +1165,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>과제1 v1 런칭 시점</t>
+          <t>06_보고서/ — 협의사항 합의 내용 반영</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RP-03</t>
+          <t>RP-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>최종 보고서</t>
+          <t>중간 보고서</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7.3조</t>
+          <t>7.3조, 10.3조(중간 검수)</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1217,14 +1217,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>전체 과업 완료 시</t>
+          <t>과제1 v1 런칭 시점</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RP-04</t>
+          <t>RP-03</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>상시</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>주간 진행 보고</t>
+          <t>최종 보고서</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>docx/메일</t>
+          <t>pptx/docx</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>매주</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 9조</t>
+          <t>7.3조</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>06_보고서/주간월간/</t>
+          <t>전체 과업 완료 시</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RP-05</t>
+          <t>RP-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>월간 진행 보고 + 정기 회의</t>
+          <t>주간 진행 보고</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>docx/메일</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>매월</t>
+          <t>매주</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 9조(월 1회 회의)</t>
+          <t>7.3조, 9조</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1328,7 +1328,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RP-06</t>
+          <t>RP-05</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>회의록·협의 기록</t>
+          <t>월간 진행 보고 + 정기 회의</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>회의 시</t>
+          <t>매월</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>양측</t>
+          <t>SeekersLab</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14조(협의 서면 기록)</t>
+          <t>7.3조, 9조(월 1회 회의)</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1373,14 +1373,14 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>07_회의록/</t>
+          <t>06_보고서/주간월간/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RP-07</t>
+          <t>RP-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>변경 관리 문서</t>
+          <t>회의록·협의 기록</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>변경 발생 시</t>
+          <t>회의 시</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14조(변경 관리 절차)</t>
+          <t>14조(협의 서면 기록)</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1432,42 +1432,42 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RP-08</t>
+          <t>RP-07</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공통 보고</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>상시</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>소스코드 일체 인도</t>
+          <t>변경 관리 문서</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>변경 발생 시</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>양측</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 9조</t>
+          <t>14조(변경 관리 절차)</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1477,14 +1477,14 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Git 저장소</t>
+          <t>07_회의록/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RP-09</t>
+          <t>RP-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>데이터 삭제 확인서</t>
+          <t>소스코드 일체 인도</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>계약 종료 시</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11조</t>
+          <t>7.3조, 9조</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1529,29 +1529,29 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>제공 데이터 삭제 서면 확인</t>
+          <t>Git 저장소</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D1-01</t>
+          <t>RP-09</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>과제1</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>진단(4월)</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>서비스 수준 진단 보고서</t>
+          <t>데이터 삭제 확인서</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>계약 종료 시</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4.1.1조</t>
+          <t>11조</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>OCR 인식률·vLLM 정확도·Latency/Throughput 측정</t>
+          <t>제공 데이터 삭제 서면 확인</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D1-02</t>
+          <t>D1-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>상품화 요건 정의서 (최소/목표 사양)</t>
+          <t>서비스 수준 진단 보고서</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1633,14 +1633,14 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>FVT 정량 기준의 원천</t>
+          <t>OCR 인식률·vLLM 정확도·Latency/Throughput 측정</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>D1-03</t>
+          <t>D1-02</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>프롬프트(4~5월)</t>
+          <t>진단(4월)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 개선 보고서 (전후 비교)</t>
+          <t>상품화 요건 정의서 (최소/목표 사양)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4.1.2조</t>
+          <t>4.1.1조</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1683,12 +1683,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>FVT 정량 기준의 원천</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D1-04</t>
+          <t>D1-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1703,7 +1707,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 가이드라인</t>
+          <t>프롬프트 개선 보고서 (전후 비교)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1731,16 +1735,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>버전 관리 체계 포함</t>
-        </is>
-      </c>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>D1-05</t>
+          <t>D1-04</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>최적화(5~6월)</t>
+          <t>프롬프트(4~5월)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>성능 최적화 보고서</t>
+          <t>프롬프트 가이드라인</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4.1.3조</t>
+          <t>4.1.2조</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -1785,14 +1785,14 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>병목 분석·최적화 결과·사양 달성 현황</t>
+          <t>버전 관리 체계 포함</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D1-06</t>
+          <t>D1-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>패키징(6월)</t>
+          <t>최적화(5~6월)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>배포 패키지 (컨테이너 이미지·스크립트)</t>
+          <t>성능 최적화 보고서</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>산출물</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4.1.4조</t>
+          <t>4.1.3조</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1837,14 +1837,14 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Helm Chart 또는 Docker Compose</t>
+          <t>병목 분석·최적화 결과·사양 달성 현황</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D1-07</t>
+          <t>D1-06</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>API 문서 (OpenAPI/Swagger)</t>
+          <t>배포 패키지 (컨테이너 이미지·스크립트)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>yaml/html</t>
+          <t>산출물</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1887,12 +1887,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Helm Chart 또는 Docker Compose</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D1-08</t>
+          <t>D1-07</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1907,12 +1911,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>운영 매뉴얼</t>
+          <t>API 문서 (OpenAPI/Swagger)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>yaml/html</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1935,16 +1939,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>설치·설정·모니터링·장애 대응</t>
-        </is>
-      </c>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>D1-09</t>
+          <t>D1-08</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>v1 런칭(7월)</t>
+          <t>패키징(6월)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>v1 릴리즈 노트</t>
+          <t>운영 매뉴얼</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4.1.5조</t>
+          <t>4.1.4조</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -1987,12 +1987,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>설치·설정·모니터링·장애 대응</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>D1-10</t>
+          <t>D1-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2007,12 +2011,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>테스트 결과 보고서</t>
+          <t>v1 릴리즈 노트</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>docx/xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2035,16 +2039,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>기능·성능·부하 테스트</t>
-        </is>
-      </c>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>D1-11</t>
+          <t>D1-10</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>최소/목표 사양 달성 보고서</t>
+          <t>테스트 결과 보고서</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>docx/xlsx</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2089,29 +2089,29 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>인수 기준 입증 문서</t>
+          <t>기능·성능·부하 테스트</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>D2-01</t>
+          <t>D1-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>과제2</t>
+          <t>과제1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>요건(4~5월)</t>
+          <t>v1 런칭(7월)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>요건 정의서 (기능/비기능/데이터)</t>
+          <t>최소/목표 사양 달성 보고서</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4.2.1조</t>
+          <t>4.1.5조</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>IN-02 초안 기반 확장</t>
+          <t>인수 기준 입증 문서</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D2-02</t>
+          <t>D2-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>설계(5월)</t>
+          <t>요건(4~5월)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>시스템 설계서 (아키텍처)</t>
+          <t>요건 정의서 (기능/비기능/데이터)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4.2.2조</t>
+          <t>4.2.1조</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2191,12 +2191,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>IN-02 초안 기반 확장</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D2-03</t>
+          <t>D2-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2211,7 +2215,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>데이터 파이프라인 설계서</t>
+          <t>시스템 설계서 (아키텍처)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2239,16 +2243,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>ETL/Streaming/Feature Store</t>
-        </is>
-      </c>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D2-04</t>
+          <t>D2-03</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>인터페이스 정의서</t>
+          <t>데이터 파이프라인 설계서</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>docx/xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2293,14 +2293,14 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>REST API/Event Bus/Webhook</t>
+          <t>ETL/Streaming/Feature Store</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D2-05</t>
+          <t>D2-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>개발(6~8월)</t>
+          <t>설계(5월)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>개발 모듈 + 단위 테스트 결과</t>
+          <t>인터페이스 정의서</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>소스+docx</t>
+          <t>docx/xlsx</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4.2.3조</t>
+          <t>4.2.2조</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -2345,14 +2345,14 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>예측·동적임계치·RCA·LLM·대응추천</t>
+          <t>REST API/Event Bus/Webhook</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D2-06</t>
+          <t>D2-05</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>모듈화(8~9월)</t>
+          <t>개발(6~8월)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>알림 모듈 (독립 배포 패키지)</t>
+          <t>개발 모듈 + 단위 테스트 결과</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>산출물</t>
+          <t>소스+docx</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4.2.4조</t>
+          <t>4.2.3조</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -2397,14 +2397,14 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>표준 인터페이스 명세 포함</t>
+          <t>예측·동적임계치·RCA·LLM·대응추천</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>D2-07</t>
+          <t>D2-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2414,22 +2414,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>테스트(9~10월)</t>
+          <t>모듈화(8~9월)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>통합 테스트 결과 보고서</t>
+          <t>알림 모듈 (독립 배포 패키지)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>docx/xlsx</t>
+          <t>산출물</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4.2.5조, 10.3조(중간 검수)</t>
+          <t>4.2.4조</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -2449,14 +2449,14 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>EWACS 연동·성능</t>
+          <t>표준 인터페이스 명세 포함</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>D2-08</t>
+          <t>D2-07</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>안정화(11~12월)</t>
+          <t>테스트(9~10월)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>운영 가이드</t>
+          <t>통합 테스트 결과 보고서</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>docx/xlsx</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4.2.6조</t>
+          <t>4.2.5조, 10.3조(중간 검수)</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -2499,12 +2499,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>EWACS 연동·성능</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>D2-09</t>
+          <t>D2-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2519,12 +2523,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>교육 자료</t>
+          <t>운영 가이드</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2547,16 +2551,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>운영자 교육</t>
-        </is>
-      </c>
+      <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>D2-10</t>
+          <t>D2-09</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>인수인계 문서</t>
+          <t>교육 자료</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2599,64 +2599,64 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>운영자 교육</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CU-01</t>
+          <t>D2-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CUPIA 제공</t>
+          <t>과제2</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>착수 전</t>
+          <t>안정화(11~12월)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>익명화 데이터 (신고서 샘플 등)</t>
+          <t>인수인계 문서</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>착수 시</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>CUPIA</t>
+          <t>SeekersLab</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8조</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>수령 예정</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>범위·익명화 수준 협의 필요</t>
-        </is>
-      </c>
+          <t>4.2.6조</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CU-02</t>
+          <t>CU-01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>OCR+vLLM 시스템 코드·프롬프트·모델 정보</t>
+          <t>익명화 데이터 (신고서 샘플 등)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>공유 범위 협의 필요</t>
+          <t>범위·익명화 수준 협의 필요</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CU-03</t>
+          <t>CU-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>EWACS 현행 시스템 문서·접근 권한</t>
+          <t>OCR+vLLM 시스템 코드·프롬프트·모델 정보</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2753,57 +2753,109 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>담당자 지정 포함</t>
+          <t>공유 범위 협의 필요</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>CU-03</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CUPIA 제공</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>착수 전</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>EWACS 현행 시스템 문서·접근 권한</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>착수 시</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>CUPIA</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>8조</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>수령 예정</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>담당자 지정 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>CU-04</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>CUPIA 제공</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>착수 전</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>개발/테스트 인프라 (GPU 포함)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>착수 시</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>CUPIA</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>8조</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>협의 예정</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>클라우드 사용 협의 가능</t>
         </is>

--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -808,59 +808,59 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IN-01</t>
+          <t>CT-06</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>내부</t>
+          <t>계약</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>착수 전</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>제안서</t>
+          <t>수의계약 사유서 (세칙 제33조 1항 1호)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>계약 협상 전</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>SeekersLab 초안 → CUPIA 확정</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>초안 v0.3</t>
+          <t>세칙 제33조·제36조</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>초안 v0.1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>01_제안서/ — 라이트 컨설팅 스타일 (12슬라이드)</t>
+          <t>08_계약관리/ — 실적 증빙(근거자료 5번) 보완 필요</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>IN-02</t>
+          <t>IN-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -870,22 +870,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>준비</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>요구사항 정의서(통합)</t>
+          <t>제안서</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>상시 갱신</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -900,19 +900,19 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>초안 v0.1</t>
+          <t>초안 v0.3</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>02_요구사항/ — 과제2 요건 정의서(D2-01)의 기초</t>
+          <t>01_제안서/ — 라이트 컨설팅 스타일 (12슬라이드)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>IN-03</t>
+          <t>IN-02</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>기능확인서 (FVT)</t>
+          <t>요구사항 정의서(통합)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>검수 시</t>
+          <t>상시 갱신</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10조 인수 기준</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -957,14 +957,14 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>03_기능확인서_FVT/ — 18항목</t>
+          <t>02_요구사항/ — 과제2 요건 정의서(D2-01)의 기초</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>IN-04</t>
+          <t>IN-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>WBS / 일정계획</t>
+          <t>기능확인서 (FVT)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>착수 시</t>
+          <t>검수 시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5조</t>
+          <t>10조 인수 기준</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1009,14 +1009,14 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>04_WBS/</t>
+          <t>03_기능확인서_FVT/ — 18항목</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>IN-05</t>
+          <t>IN-04</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>시스템 구성요소·기능 정의서 (과제1/2)</t>
+          <t>WBS / 일정계획</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>상시 갱신</t>
+          <t>착수 시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5조</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1061,14 +1061,14 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>05_시스템구성/</t>
+          <t>04_WBS/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IN-06</t>
+          <t>IN-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>계약 준비</t>
+          <t>준비</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>계약 가이드라인 (CUPIA 계약관리 시행세칙 적용 기준)</t>
+          <t>시스템 구성요소·기능 정의서 (과제1/2)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>계약 협상 전</t>
+          <t>상시 갱신</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>세칙 제3~12조·제33조</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1113,39 +1113,39 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>08_계약관리/ — 세칙 원문은 reference/04</t>
+          <t>05_시스템구성/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RP-01</t>
+          <t>IN-06</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>공통 보고</t>
+          <t>내부</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>착수</t>
+          <t>계약 준비</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>착수 보고서</t>
+          <t>계약 가이드라인 (CUPIA 계약관리 시행세칙 적용 기준)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>pptx/docx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>계약 협상 전</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1155,24 +1155,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7.3조</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>세칙 제3~12조·제33조</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>초안 v0.1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>06_보고서/ — 협의사항 합의 내용 반영</t>
+          <t>08_계약관리/ — 세칙 원문은 reference/04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RP-02</t>
+          <t>RP-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>착수</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>중간 보고서</t>
+          <t>착수 보고서</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 10.3조(중간 검수)</t>
+          <t>7.3조</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1217,14 +1217,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>과제1 v1 런칭 시점</t>
+          <t>06_보고서/ — 협의사항 합의 내용 반영</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RP-03</t>
+          <t>RP-02</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>최종 보고서</t>
+          <t>중간 보고서</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7.3조</t>
+          <t>7.3조, 10.3조(중간 검수)</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>전체 과업 완료 시</t>
+          <t>과제1 v1 런칭 시점</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RP-04</t>
+          <t>RP-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1286,22 +1286,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>상시</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>주간 진행 보고</t>
+          <t>최종 보고서</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>docx/메일</t>
+          <t>pptx/docx</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>매주</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 9조</t>
+          <t>7.3조</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1321,14 +1321,14 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>06_보고서/주간월간/</t>
+          <t>전체 과업 완료 시</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RP-05</t>
+          <t>RP-04</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>월간 진행 보고 + 정기 회의</t>
+          <t>주간 진행 보고</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>docx/메일</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>매월</t>
+          <t>매주</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 9조(월 1회 회의)</t>
+          <t>7.3조, 9조</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RP-06</t>
+          <t>RP-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>회의록·협의 기록</t>
+          <t>월간 진행 보고 + 정기 회의</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>회의 시</t>
+          <t>매월</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>양측</t>
+          <t>SeekersLab</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14조(협의 서면 기록)</t>
+          <t>7.3조, 9조(월 1회 회의)</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1425,14 +1425,14 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>07_회의록/</t>
+          <t>06_보고서/주간월간/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RP-07</t>
+          <t>RP-06</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>변경 관리 문서</t>
+          <t>회의록·협의 기록</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>변경 발생 시</t>
+          <t>회의 시</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14조(변경 관리 절차)</t>
+          <t>14조(협의 서면 기록)</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1484,42 +1484,42 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RP-08</t>
+          <t>RP-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>공통 보고</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>종료</t>
+          <t>상시</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>소스코드 일체 인도</t>
+          <t>변경 관리 문서</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>변경 발생 시</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>양측</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7.3조, 9조</t>
+          <t>14조(변경 관리 절차)</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1529,14 +1529,14 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Git 저장소</t>
+          <t>07_회의록/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RP-09</t>
+          <t>RP-08</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>데이터 삭제 확인서</t>
+          <t>소스코드 일체 인도</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>계약 종료 시</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11조</t>
+          <t>7.3조, 9조</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1581,29 +1581,29 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>제공 데이터 삭제 서면 확인</t>
+          <t>Git 저장소</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D1-01</t>
+          <t>RP-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>과제1</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>진단(4월)</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>서비스 수준 진단 보고서</t>
+          <t>데이터 삭제 확인서</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>계약 종료 시</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4.1.1조</t>
+          <t>11조</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1633,14 +1633,14 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>OCR 인식률·vLLM 정확도·Latency/Throughput 측정</t>
+          <t>제공 데이터 삭제 서면 확인</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>D1-02</t>
+          <t>D1-01</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>상품화 요건 정의서 (최소/목표 사양)</t>
+          <t>서비스 수준 진단 보고서</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>FVT 정량 기준의 원천</t>
+          <t>OCR 인식률·vLLM 정확도·Latency/Throughput 측정</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D1-03</t>
+          <t>D1-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>프롬프트(4~5월)</t>
+          <t>진단(4월)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 개선 보고서 (전후 비교)</t>
+          <t>상품화 요건 정의서 (최소/목표 사양)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4.1.2조</t>
+          <t>4.1.1조</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -1735,12 +1735,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>FVT 정량 기준의 원천</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>D1-04</t>
+          <t>D1-03</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1755,7 +1759,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>프롬프트 가이드라인</t>
+          <t>프롬프트 개선 보고서 (전후 비교)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1783,16 +1787,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>버전 관리 체계 포함</t>
-        </is>
-      </c>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D1-05</t>
+          <t>D1-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>최적화(5~6월)</t>
+          <t>프롬프트(4~5월)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>성능 최적화 보고서</t>
+          <t>프롬프트 가이드라인</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4.1.3조</t>
+          <t>4.1.2조</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1837,14 +1837,14 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>병목 분석·최적화 결과·사양 달성 현황</t>
+          <t>버전 관리 체계 포함</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D1-06</t>
+          <t>D1-05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1854,17 +1854,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>패키징(6월)</t>
+          <t>최적화(5~6월)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>배포 패키지 (컨테이너 이미지·스크립트)</t>
+          <t>성능 최적화 보고서</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>산출물</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4.1.4조</t>
+          <t>4.1.3조</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -1889,14 +1889,14 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Helm Chart 또는 Docker Compose</t>
+          <t>병목 분석·최적화 결과·사양 달성 현황</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D1-07</t>
+          <t>D1-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>API 문서 (OpenAPI/Swagger)</t>
+          <t>배포 패키지 (컨테이너 이미지·스크립트)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>yaml/html</t>
+          <t>산출물</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1939,12 +1939,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Helm Chart 또는 Docker Compose</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>D1-08</t>
+          <t>D1-07</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1959,12 +1963,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>운영 매뉴얼</t>
+          <t>API 문서 (OpenAPI/Swagger)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>yaml/html</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1987,16 +1991,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>설치·설정·모니터링·장애 대응</t>
-        </is>
-      </c>
+      <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>D1-09</t>
+          <t>D1-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>v1 런칭(7월)</t>
+          <t>패키징(6월)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>v1 릴리즈 노트</t>
+          <t>운영 매뉴얼</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4.1.5조</t>
+          <t>4.1.4조</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2039,12 +2039,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>설치·설정·모니터링·장애 대응</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>D1-10</t>
+          <t>D1-09</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2059,12 +2063,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>테스트 결과 보고서</t>
+          <t>v1 릴리즈 노트</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>docx/xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2087,16 +2091,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>기능·성능·부하 테스트</t>
-        </is>
-      </c>
+      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>D1-11</t>
+          <t>D1-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>최소/목표 사양 달성 보고서</t>
+          <t>테스트 결과 보고서</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>docx/xlsx</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2141,29 +2141,29 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>인수 기준 입증 문서</t>
+          <t>기능·성능·부하 테스트</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D2-01</t>
+          <t>D1-11</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>과제2</t>
+          <t>과제1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>요건(4~5월)</t>
+          <t>v1 런칭(7월)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>요건 정의서 (기능/비기능/데이터)</t>
+          <t>최소/목표 사양 달성 보고서</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4.2.1조</t>
+          <t>4.1.5조</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>IN-02 초안 기반 확장</t>
+          <t>인수 기준 입증 문서</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D2-02</t>
+          <t>D2-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>설계(5월)</t>
+          <t>요건(4~5월)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>시스템 설계서 (아키텍처)</t>
+          <t>요건 정의서 (기능/비기능/데이터)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4.2.2조</t>
+          <t>4.2.1조</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2243,12 +2243,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>IN-02 초안 기반 확장</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D2-03</t>
+          <t>D2-02</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2263,7 +2267,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>데이터 파이프라인 설계서</t>
+          <t>시스템 설계서 (아키텍처)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2291,16 +2295,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>ETL/Streaming/Feature Store</t>
-        </is>
-      </c>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D2-04</t>
+          <t>D2-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>인터페이스 정의서</t>
+          <t>데이터 파이프라인 설계서</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>docx/xlsx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2345,14 +2345,14 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>REST API/Event Bus/Webhook</t>
+          <t>ETL/Streaming/Feature Store</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D2-05</t>
+          <t>D2-04</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>개발(6~8월)</t>
+          <t>설계(5월)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>개발 모듈 + 단위 테스트 결과</t>
+          <t>인터페이스 정의서</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>소스+docx</t>
+          <t>docx/xlsx</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4.2.3조</t>
+          <t>4.2.2조</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -2397,14 +2397,14 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>예측·동적임계치·RCA·LLM·대응추천</t>
+          <t>REST API/Event Bus/Webhook</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>D2-06</t>
+          <t>D2-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2414,22 +2414,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>모듈화(8~9월)</t>
+          <t>개발(6~8월)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>알림 모듈 (독립 배포 패키지)</t>
+          <t>개발 모듈 + 단위 테스트 결과</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>산출물</t>
+          <t>소스+docx</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4.2.4조</t>
+          <t>4.2.3조</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -2449,14 +2449,14 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>표준 인터페이스 명세 포함</t>
+          <t>예측·동적임계치·RCA·LLM·대응추천</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>D2-07</t>
+          <t>D2-06</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>테스트(9~10월)</t>
+          <t>모듈화(8~9월)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>통합 테스트 결과 보고서</t>
+          <t>알림 모듈 (독립 배포 패키지)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>docx/xlsx</t>
+          <t>산출물</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4.2.5조, 10.3조(중간 검수)</t>
+          <t>4.2.4조</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>EWACS 연동·성능</t>
+          <t>표준 인터페이스 명세 포함</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>D2-08</t>
+          <t>D2-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>안정화(11~12월)</t>
+          <t>테스트(9~10월)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>운영 가이드</t>
+          <t>통합 테스트 결과 보고서</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>docx/xlsx</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4.2.6조</t>
+          <t>4.2.5조, 10.3조(중간 검수)</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -2551,12 +2551,16 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>EWACS 연동·성능</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>D2-09</t>
+          <t>D2-08</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2571,12 +2575,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>교육 자료</t>
+          <t>운영 가이드</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2599,16 +2603,12 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>운영자 교육</t>
-        </is>
-      </c>
+      <c r="J41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>D2-10</t>
+          <t>D2-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>인수인계 문서</t>
+          <t>교육 자료</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2651,64 +2651,64 @@
           <t>예정</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>운영자 교육</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CU-01</t>
+          <t>D2-10</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CUPIA 제공</t>
+          <t>과제2</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>착수 전</t>
+          <t>안정화(11~12월)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>익명화 데이터 (신고서 샘플 등)</t>
+          <t>인수인계 문서</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>착수 시</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>CUPIA</t>
+          <t>SeekersLab</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8조</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>수령 예정</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>범위·익명화 수준 협의 필요</t>
-        </is>
-      </c>
+          <t>4.2.6조</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CU-02</t>
+          <t>CU-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>OCR+vLLM 시스템 코드·프롬프트·모델 정보</t>
+          <t>익명화 데이터 (신고서 샘플 등)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2753,14 +2753,14 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>공유 범위 협의 필요</t>
+          <t>범위·익명화 수준 협의 필요</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CU-03</t>
+          <t>CU-02</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>EWACS 현행 시스템 문서·접근 권한</t>
+          <t>OCR+vLLM 시스템 코드·프롬프트·모델 정보</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2805,57 +2805,109 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>담당자 지정 포함</t>
+          <t>공유 범위 협의 필요</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>CU-03</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CUPIA 제공</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>착수 전</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>EWACS 현행 시스템 문서·접근 권한</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>착수 시</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>CUPIA</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>8조</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>수령 예정</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>담당자 지정 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>CU-04</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>CUPIA 제공</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>착수 전</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>개발/테스트 인프라 (GPU 포함)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>착수 시</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>CUPIA</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>8조</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>협의 예정</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>클라우드 사용 협의 가능</t>
         </is>

--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -692,12 +692,12 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>초안 20260731 (과제2 한정)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CUPIA 예산 확인 후 — M/M 단가표 포함</t>
+          <t>08_계약관리/ — 22 M/M·193,481,808원(VAT별도), 양식: reference/05, 과제1은 수행 완료로 제외</t>
         </is>
       </c>
     </row>

--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab 인력</t>
+          <t>씨커스 인력</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab 초안 → CUPIA 확정</t>
+          <t>씨커스 초안 → CUPIA 확정</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>SeekersLab</t>
+          <t>씨커스</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2958,6 +2958,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>

--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>08_계약관리/ — 22 M/M·193,481,808원(VAT별도), 양식: reference/05, 과제1은 수행 완료로 제외</t>
+          <t>08_계약관리/ — 견적서 2종(_1 인력 M/M·_2 업무 정액, 총액 동일 193,481,808원 VAT별도), 양식: reference/05, 과제1은 수행 완료로 제외</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>

--- a/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
+++ b/cupia-ai-research/docs/00_산출물관리/산출물_관리대장_v0.1.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>08_계약관리/ — 견적서 2종(_1 인력 M/M·_2 업무 정액, 총액 동일 193,481,808원 VAT별도), 양식: reference/05, 과제1은 수행 완료로 제외</t>
+          <t>08_계약관리/ — 견적서 2종(_1 인력 M/M·_2 업무 정액, 총액 동일 220,000,000원 VAT별도, 인건비 193.5M+일반관리비 6%+이윤 7.27%), 양식: reference/05, 과제1은 수행 완료로 제외</t>
         </is>
       </c>
     </row>
